--- a/Aula10/cadastro.xlsx
+++ b/Aula10/cadastro.xlsx
@@ -431,12 +431,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>heloisa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>23</t>
         </is>
       </c>
     </row>
